--- a/data/Pokerbilanz.xlsx
+++ b/data/Pokerbilanz.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986c3747c471c36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legol\OneDrive\Dokumente\Coding Projekte\PokerDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="11_05CB57645360D2BE9564E5F22174A2074E73379C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4F14CCC-5325-4F86-AB50-5316D9E36376}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="374">
   <si>
     <t>Julius</t>
   </si>
@@ -1157,6 +1157,9 @@
   </si>
   <si>
     <t>12.06.2026</t>
+  </si>
+  <si>
+    <t>26.06.2026</t>
   </si>
 </sst>
 </file>
@@ -6805,7 +6808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ201"/>
+  <dimension ref="A1:AZ202"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
@@ -20333,7 +20336,7 @@
         <v>363</v>
       </c>
       <c r="AZ194">
-        <f t="shared" ref="AZ194:AZ201" si="0">SUM(A194:AX194)</f>
+        <f t="shared" ref="AZ194:AZ202" si="0">SUM(A194:AX194)</f>
         <v>5.0000000000004263E-2</v>
       </c>
     </row>
@@ -20527,6 +20530,33 @@
       <c r="AZ201">
         <f t="shared" si="0"/>
         <v>-0.20000000000000284</v>
+      </c>
+    </row>
+    <row r="202" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B202" s="2">
+        <v>54.5</v>
+      </c>
+      <c r="C202" s="2">
+        <v>22.7</v>
+      </c>
+      <c r="D202">
+        <v>27.2</v>
+      </c>
+      <c r="H202">
+        <v>-21.5</v>
+      </c>
+      <c r="T202" s="2">
+        <v>-51.5</v>
+      </c>
+      <c r="AQ202">
+        <v>-31.5</v>
+      </c>
+      <c r="AY202" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="AZ202">
+        <f t="shared" si="0"/>
+        <v>-9.9999999999994316E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Pokerbilanz.xlsx
+++ b/data/Pokerbilanz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legol\OneDrive\Dokumente\Coding Projekte\PokerDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986c3747c471c36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A910C643-45D3-4E76-98E6-5E16D120E7AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="375">
   <si>
     <t>Julius</t>
   </si>
@@ -1160,6 +1160,9 @@
   </si>
   <si>
     <t>26.06.2026</t>
+  </si>
+  <si>
+    <t>24.07.2026</t>
   </si>
 </sst>
 </file>
@@ -6808,7 +6811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ202"/>
+  <dimension ref="A1:AZ203"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
@@ -20336,7 +20339,7 @@
         <v>363</v>
       </c>
       <c r="AZ194">
-        <f t="shared" ref="AZ194:AZ202" si="0">SUM(A194:AX194)</f>
+        <f t="shared" ref="AZ194:AZ203" si="0">SUM(A194:AX194)</f>
         <v>5.0000000000004263E-2</v>
       </c>
     </row>
@@ -20557,6 +20560,39 @@
       <c r="AZ202">
         <f t="shared" si="0"/>
         <v>-9.9999999999994316E-2</v>
+      </c>
+    </row>
+    <row r="203" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B203" s="2">
+        <v>-20</v>
+      </c>
+      <c r="C203" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="D203">
+        <v>-2.6</v>
+      </c>
+      <c r="L203" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="T203" s="2">
+        <v>-20</v>
+      </c>
+      <c r="AE203">
+        <v>-7.6</v>
+      </c>
+      <c r="AM203">
+        <v>-11.5</v>
+      </c>
+      <c r="AR203">
+        <v>29</v>
+      </c>
+      <c r="AY203" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="AZ203">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Pokerbilanz.xlsx
+++ b/data/Pokerbilanz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986c3747c471c36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A910C643-45D3-4E76-98E6-5E16D120E7AA}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E621A63D-DE6B-407E-A9E4-840B1FA57DB0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="376">
   <si>
     <t>Julius</t>
   </si>
@@ -1163,6 +1163,9 @@
   </si>
   <si>
     <t>24.07.2026</t>
+  </si>
+  <si>
+    <t>01.08.2026</t>
   </si>
 </sst>
 </file>
@@ -6811,7 +6814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ203"/>
+  <dimension ref="A1:AZ204"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
@@ -20339,7 +20342,7 @@
         <v>363</v>
       </c>
       <c r="AZ194">
-        <f t="shared" ref="AZ194:AZ203" si="0">SUM(A194:AX194)</f>
+        <f t="shared" ref="AZ194:AZ204" si="0">SUM(A194:AX194)</f>
         <v>5.0000000000004263E-2</v>
       </c>
     </row>
@@ -20591,6 +20594,30 @@
         <v>374</v>
       </c>
       <c r="AZ203">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="C204" s="2">
+        <v>-50</v>
+      </c>
+      <c r="T204" s="2">
+        <v>120</v>
+      </c>
+      <c r="W204">
+        <v>-18.399999999999999</v>
+      </c>
+      <c r="AM204">
+        <v>-30</v>
+      </c>
+      <c r="AX204">
+        <v>-21.6</v>
+      </c>
+      <c r="AY204" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="AZ204">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/data/Pokerbilanz.xlsx
+++ b/data/Pokerbilanz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986c3747c471c36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E621A63D-DE6B-407E-A9E4-840B1FA57DB0}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F536347-9D79-4252-BD9A-4C8177374C32}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="377">
   <si>
     <t>Julius</t>
   </si>
@@ -1165,7 +1165,10 @@
     <t>24.07.2026</t>
   </si>
   <si>
-    <t>01.08.2026</t>
+    <t>07.08.2026</t>
+  </si>
+  <si>
+    <t>31.07.2026</t>
   </si>
 </sst>
 </file>
@@ -6814,7 +6817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ204"/>
+  <dimension ref="A1:AZ205"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
@@ -20342,7 +20345,7 @@
         <v>363</v>
       </c>
       <c r="AZ194">
-        <f t="shared" ref="AZ194:AZ204" si="0">SUM(A194:AX194)</f>
+        <f t="shared" ref="AZ194:AZ205" si="0">SUM(A194:AX194)</f>
         <v>5.0000000000004263E-2</v>
       </c>
     </row>
@@ -20615,9 +20618,42 @@
         <v>-21.6</v>
       </c>
       <c r="AY204" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="AZ204">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B205" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="C205" s="2">
+        <v>69</v>
+      </c>
+      <c r="D205">
+        <v>54.6</v>
+      </c>
+      <c r="T205" s="2">
+        <v>-60</v>
+      </c>
+      <c r="W205">
+        <v>-8.6999999999999993</v>
+      </c>
+      <c r="AM205">
+        <v>110</v>
+      </c>
+      <c r="AQ205">
+        <v>-149.19999999999999</v>
+      </c>
+      <c r="AX205">
+        <v>-40</v>
+      </c>
+      <c r="AY205" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="AZ204">
+      <c r="AZ205">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/data/Pokerbilanz.xlsx
+++ b/data/Pokerbilanz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986c3747c471c36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986C3747C471C36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F536347-9D79-4252-BD9A-4C8177374C32}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1EA8385-204C-4B3B-9C44-099213417ED2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="378">
   <si>
     <t>Julius</t>
   </si>
@@ -1169,6 +1169,9 @@
   </si>
   <si>
     <t>31.07.2026</t>
+  </si>
+  <si>
+    <t>28.08.2026</t>
   </si>
 </sst>
 </file>
@@ -6817,7 +6820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ205"/>
+  <dimension ref="A1:AZ206"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
@@ -20345,7 +20348,7 @@
         <v>363</v>
       </c>
       <c r="AZ194">
-        <f t="shared" ref="AZ194:AZ205" si="0">SUM(A194:AX194)</f>
+        <f t="shared" ref="AZ194:AZ206" si="0">SUM(A194:AX194)</f>
         <v>5.0000000000004263E-2</v>
       </c>
     </row>
@@ -20656,6 +20659,33 @@
       <c r="AZ205">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B206" s="2">
+        <v>-23.8</v>
+      </c>
+      <c r="L206">
+        <v>-3.6</v>
+      </c>
+      <c r="T206" s="2">
+        <v>-0.2</v>
+      </c>
+      <c r="AE206">
+        <v>72.599999999999994</v>
+      </c>
+      <c r="AM206">
+        <v>-30.1</v>
+      </c>
+      <c r="AR206">
+        <v>-13</v>
+      </c>
+      <c r="AY206" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AZ206">
+        <f t="shared" si="0"/>
+        <v>1.8999999999999915</v>
       </c>
     </row>
   </sheetData>

--- a/data/Pokerbilanz.xlsx
+++ b/data/Pokerbilanz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986C3747C471C36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1EA8385-204C-4B3B-9C44-099213417ED2}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6921E69B-D831-4692-82E5-BE92F3EE3184}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="379">
   <si>
     <t>Julius</t>
   </si>
@@ -1172,6 +1172,9 @@
   </si>
   <si>
     <t>28.08.2026</t>
+  </si>
+  <si>
+    <t>14.08.2026</t>
   </si>
 </sst>
 </file>
@@ -6820,7 +6823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ206"/>
+  <dimension ref="A1:AZ207"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
@@ -20348,7 +20351,7 @@
         <v>363</v>
       </c>
       <c r="AZ194">
-        <f t="shared" ref="AZ194:AZ206" si="0">SUM(A194:AX194)</f>
+        <f t="shared" ref="AZ194:AZ207" si="0">SUM(A194:AX194)</f>
         <v>5.0000000000004263E-2</v>
       </c>
     </row>
@@ -20681,11 +20684,38 @@
         <v>-13</v>
       </c>
       <c r="AY206" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AZ206">
         <f t="shared" si="0"/>
         <v>1.8999999999999915</v>
+      </c>
+    </row>
+    <row r="207" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B207" s="2">
+        <v>47.2</v>
+      </c>
+      <c r="C207" s="2">
+        <v>-40</v>
+      </c>
+      <c r="H207">
+        <v>22.4</v>
+      </c>
+      <c r="L207">
+        <v>-30</v>
+      </c>
+      <c r="AJ207">
+        <v>-20</v>
+      </c>
+      <c r="AM207">
+        <v>21.8</v>
+      </c>
+      <c r="AY207" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AZ207">
+        <f t="shared" si="0"/>
+        <v>1.4000000000000021</v>
       </c>
     </row>
   </sheetData>
